--- a/mistral_translate_work/split_by_prompt/excel/lore/lang_map_mark/lang_map_mark__lore__part_0001.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/lore/lang_map_mark/lang_map_mark__lore__part_0001.xlsx
@@ -1571,7 +1571,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Creatures Đột Biến Cỡ Lớn sinh sống sâu trong Hẻm núi Spirit, chiếc chuông cổ trên lưng chúng có thể phát nổ bằng sóng âm cực kỳ致命 khi rung lên.</t>
+          <t>Sinh vật đột biến cỡ lớn sinh sống sâu trong Hẻm núi Spirit, chiếc chuông cổ trên lưng chúng có thể phát nổ bằng sóng âm cực kỳ chí mạng khi rung lên.</t>
         </is>
       </c>
     </row>
@@ -7425,7 +7425,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Creatures Đột Biến Cỡ Lớn sinh sống sâu trong Hẻm núi Spirit, chiếc chuông cổ trên lưng chúng có thể phát nổ bằng sóng âm cực kỳ致命 khi rung lên.</t>
+          <t>Sinh vật đột biến cỡ lớn sinh sống sâu trong Hẻm núi Spirit, chiếc chuông cổ trên lưng chúng có thể phát nổ bằng sóng âm cực kỳ chí mạng khi rung lên.</t>
         </is>
       </c>
     </row>
